--- a/resources/templates/karaba/roro_contract.xlsx
+++ b/resources/templates/karaba/roro_contract.xlsx
@@ -20,7 +20,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="41">
   <si>
     <r>
-      <t xml:space="preserve">PROFORM CONTRACT</t>
+      <t xml:space="preserve">PROFORMA CONTRACT</t>
     </r>
   </si>
   <si>
@@ -53,7 +53,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Adress</t>
+      <t xml:space="preserve">Address</t>
     </r>
   </si>
   <si>
@@ -94,7 +94,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Swift Cose</t>
+      <t xml:space="preserve">Swift Code</t>
     </r>
   </si>
   <si>
@@ -102,7 +102,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Bank Adress</t>
+      <t xml:space="preserve">Bank Address</t>
     </r>
   </si>
   <si>
@@ -118,7 +118,7 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Beneficiary Adress</t>
+      <t xml:space="preserve">Beneficiary Address</t>
     </r>
   </si>
   <si>
@@ -1557,24 +1557,35 @@
       <c r="E1" s="36" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">PROFORM CONTRACT</t>
+            <t xml:space="preserve">PROFORMA CONTRACT</t>
           </r>
         </is>
       </c>
       <c r="F1" s="53"/>
       <c r="G1" s="54"/>
       <c r="H1" s="12"/>
+      <c r="I1" s="52"/>
       <c r="J1" s="52"/>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="37" t="s">
         <v>1</v>
       </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
       <c r="G2" s="4"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
       <c r="J2"/>
     </row>
     <row r="3" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
       <c r="A3" s="55"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
       <c r="E3" s="9" t="inlineStr">
         <is>
           <r>
@@ -1587,6 +1598,8 @@
         <v>0</v>
       </c>
       <c r="G3" s="56"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
       <c r="J3" s="52"/>
     </row>
     <row r="4" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
@@ -1609,10 +1622,15 @@
         </is>
       </c>
       <c r="G4" s="57"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
       <c r="J4" s="52"/>
     </row>
     <row r="5" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
       <c r="A5" s="40"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
       <c r="E5" s="9" t="inlineStr">
         <is>
           <r>
@@ -1628,23 +1646,33 @@
         </is>
       </c>
       <c r="G5" s="57"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
       <c r="J5" s="52"/>
     </row>
     <row r="6" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
       <c r="A6" s="40"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
       <c r="E6" s="9" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Adress</t>
+            <t xml:space="preserve">Address</t>
           </r>
         </is>
       </c>
       <c r="F6" s="43"/>
       <c r="G6" s="57"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
       <c r="J6" s="52"/>
     </row>
     <row r="7" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
       <c r="A7" s="40"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="52"/>
+      <c r="D7" s="52"/>
       <c r="E7" s="9" t="inlineStr">
         <is>
           <r>
@@ -1654,17 +1682,26 @@
       </c>
       <c r="F7" s="44"/>
       <c r="G7" s="57"/>
+      <c r="H7" s="52"/>
+      <c r="I7" s="52"/>
       <c r="J7" s="52"/>
     </row>
     <row r="8" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
       <c r="A8" s="40"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
       <c r="E8" s="9"/>
       <c r="F8" s="44"/>
       <c r="G8" s="57"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
       <c r="J8" s="52"/>
     </row>
     <row r="9" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A9" s="40"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
       <c r="D9" s="7"/>
       <c r="E9" s="9" t="inlineStr">
         <is>
@@ -1681,6 +1718,8 @@
         </is>
       </c>
       <c r="G9" s="57"/>
+      <c r="H9" s="52"/>
+      <c r="I9" s="52"/>
       <c r="J9" s="52"/>
     </row>
     <row r="10" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
@@ -1697,6 +1736,8 @@
       <c r="E10" s="58"/>
       <c r="F10" s="58"/>
       <c r="G10" s="59"/>
+      <c r="H10" s="52"/>
+      <c r="I10" s="52"/>
       <c r="J10" s="52"/>
     </row>
     <row r="11" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
@@ -1723,13 +1764,15 @@
         <v>15</v>
       </c>
       <c r="G11" s="60"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
       <c r="J11" s="52"/>
     </row>
     <row r="12" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A12" s="32" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Swift Cose</t>
+            <t xml:space="preserve">Swift Code</t>
           </r>
         </is>
       </c>
@@ -1741,7 +1784,7 @@
       <c r="E12" s="33" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Bank Adress</t>
+            <t xml:space="preserve">Bank Address</t>
           </r>
         </is>
       </c>
@@ -1749,6 +1792,8 @@
         <v>19</v>
       </c>
       <c r="G12" s="62"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
       <c r="J12" s="52"/>
     </row>
     <row r="13" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
@@ -1767,19 +1812,26 @@
       <c r="E13" s="51" t="inlineStr">
         <is>
           <r>
-            <t xml:space="preserve">Beneficiary Adress</t>
+            <t xml:space="preserve">Beneficiary Address</t>
           </r>
         </is>
       </c>
       <c r="F13" s="65"/>
       <c r="G13" s="66"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
       <c r="J13" s="52"/>
     </row>
     <row r="14" spans="1:10" customHeight="1" ht="13.5" s="52" customFormat="1">
       <c r="A14" s="8"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
       <c r="D14" s="7"/>
       <c r="E14" s="67"/>
+      <c r="F14" s="52"/>
       <c r="G14" s="21"/>
+      <c r="H14" s="52"/>
+      <c r="I14" s="52"/>
       <c r="J14" s="52"/>
     </row>
     <row r="15" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
@@ -1832,6 +1884,8 @@
           </r>
         </is>
       </c>
+      <c r="H15" s="52"/>
+      <c r="I15" s="52"/>
       <c r="J15" s="52"/>
     </row>
     <row r="16" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
@@ -1869,6 +1923,7 @@
       <c r="G16" s="69">
         <v>1075</v>
       </c>
+      <c r="H16" s="52"/>
       <c r="I16" s="28" t="str">
         <f>F16+G16</f>
         <v>0</v>
@@ -1910,6 +1965,7 @@
       <c r="G17" s="69">
         <v>1075</v>
       </c>
+      <c r="H17" s="52"/>
       <c r="I17" s="28" t="str">
         <f>F17+G17</f>
         <v>0</v>
@@ -1951,6 +2007,7 @@
       <c r="G18" s="69">
         <v>1075</v>
       </c>
+      <c r="H18" s="52"/>
       <c r="I18" s="28" t="str">
         <f>F18+G18</f>
         <v>0</v>
@@ -1992,6 +2049,7 @@
       <c r="G19" s="69">
         <v>1075</v>
       </c>
+      <c r="H19" s="52"/>
       <c r="I19" s="28" t="str">
         <f>F19+G19</f>
         <v>0</v>
@@ -2009,6 +2067,7 @@
       <c r="E20" s="5"/>
       <c r="F20" s="70"/>
       <c r="G20" s="71"/>
+      <c r="H20" s="52"/>
       <c r="I20" s="28" t="str">
         <f>F20+G20</f>
         <v>0</v>
@@ -2026,6 +2085,7 @@
       <c r="E21" s="5"/>
       <c r="F21" s="70"/>
       <c r="G21" s="71"/>
+      <c r="H21" s="52"/>
       <c r="I21" s="28" t="str">
         <f>F21+G21</f>
         <v>0</v>
@@ -2043,6 +2103,7 @@
       <c r="E22" s="5"/>
       <c r="F22" s="70"/>
       <c r="G22" s="71"/>
+      <c r="H22" s="52"/>
       <c r="I22" s="28" t="str">
         <f>F22+G22</f>
         <v>0</v>
@@ -2060,6 +2121,7 @@
       <c r="E23" s="5"/>
       <c r="F23" s="70"/>
       <c r="G23" s="71"/>
+      <c r="H23" s="52"/>
       <c r="I23" s="28" t="str">
         <f>F23+G23</f>
         <v>0</v>
@@ -2083,6 +2145,7 @@
       </c>
       <c r="F24" s="70"/>
       <c r="G24" s="71"/>
+      <c r="H24" s="52"/>
       <c r="I24" s="28" t="str">
         <f>F24+G24</f>
         <v>0</v>
@@ -2100,6 +2163,7 @@
       <c r="E25" s="5"/>
       <c r="F25" s="70"/>
       <c r="G25" s="71"/>
+      <c r="H25" s="52"/>
       <c r="I25" s="28" t="str">
         <f>F25+G25</f>
         <v>0</v>
@@ -2483,6 +2547,7 @@
         <v>0</v>
       </c>
       <c r="G46" s="75"/>
+      <c r="H46" s="52"/>
       <c r="I46" s="28" t="str">
         <f>SUM(F16:F45)</f>
         <v>0</v>
@@ -2515,6 +2580,7 @@
         </is>
       </c>
       <c r="G47" s="75"/>
+      <c r="H47" s="52"/>
       <c r="I47" s="28" t="str">
         <f>SUM(G16:G45)</f>
         <v>0</v>
@@ -2541,6 +2607,8 @@
         </is>
       </c>
       <c r="G48" s="75"/>
+      <c r="H48" s="52"/>
+      <c r="I48" s="52"/>
       <c r="J48" s="52"/>
     </row>
     <row r="49" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2551,6 +2619,8 @@
       <c r="E49" s="23"/>
       <c r="F49" s="76"/>
       <c r="G49" s="60"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="52"/>
       <c r="J49" s="52"/>
     </row>
     <row r="50" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2561,6 +2631,8 @@
       <c r="E50" s="23"/>
       <c r="F50" s="76"/>
       <c r="G50" s="60"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="52"/>
       <c r="J50" s="52"/>
     </row>
     <row r="51" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2571,6 +2643,8 @@
       <c r="E51" s="24"/>
       <c r="F51" s="76"/>
       <c r="G51" s="60"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="52"/>
       <c r="J51" s="52"/>
     </row>
     <row r="52" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
@@ -2590,6 +2664,8 @@
         <v>0</v>
       </c>
       <c r="G52" s="75"/>
+      <c r="H52" s="52"/>
+      <c r="I52" s="52"/>
       <c r="J52" s="52"/>
     </row>
     <row r="53" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2612,6 +2688,8 @@
       </c>
       <c r="F53" s="77"/>
       <c r="G53" s="75"/>
+      <c r="H53" s="52"/>
+      <c r="I53" s="52"/>
       <c r="J53" s="52"/>
     </row>
     <row r="54" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2622,6 +2700,8 @@
       <c r="E54" s="26"/>
       <c r="F54" s="77"/>
       <c r="G54" s="75"/>
+      <c r="H54" s="52"/>
+      <c r="I54" s="52"/>
       <c r="J54" s="52"/>
     </row>
     <row r="55" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2632,6 +2712,8 @@
       <c r="E55" s="26"/>
       <c r="F55" s="77"/>
       <c r="G55" s="75"/>
+      <c r="H55" s="52"/>
+      <c r="I55" s="52"/>
       <c r="J55" s="52"/>
     </row>
     <row r="56" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2642,6 +2724,8 @@
       <c r="E56" s="26"/>
       <c r="F56" s="77"/>
       <c r="G56" s="75"/>
+      <c r="H56" s="52"/>
+      <c r="I56" s="52"/>
       <c r="J56" s="52"/>
     </row>
     <row r="57" spans="1:10" customHeight="1" ht="15.95" s="52" customFormat="1">
@@ -2652,6 +2736,8 @@
       <c r="E57" s="26"/>
       <c r="F57" s="77"/>
       <c r="G57" s="75"/>
+      <c r="H57" s="52"/>
+      <c r="I57" s="52"/>
       <c r="J57" s="52"/>
     </row>
     <row r="58" spans="1:10" customHeight="1" ht="24.95" s="52" customFormat="1">
@@ -2671,11 +2757,16 @@
         <v>0</v>
       </c>
       <c r="G58" s="78"/>
+      <c r="H58" s="52"/>
+      <c r="I58" s="52"/>
       <c r="J58" s="52"/>
     </row>
     <row r="59" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A59" s="40"/>
       <c r="B59" s="52"/>
+      <c r="C59" s="52"/>
+      <c r="D59" s="52"/>
+      <c r="E59" s="52"/>
       <c r="F59" s="41" t="inlineStr">
         <is>
           <r>
@@ -2684,26 +2775,56 @@
         </is>
       </c>
       <c r="G59" s="4"/>
+      <c r="H59" s="52"/>
+      <c r="I59" s="52"/>
       <c r="J59" s="52"/>
     </row>
     <row r="60" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A60" s="40"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="52"/>
+      <c r="D60" s="52"/>
+      <c r="E60" s="52"/>
+      <c r="F60" s="52"/>
       <c r="G60" s="4"/>
+      <c r="H60" s="52"/>
+      <c r="I60" s="52"/>
       <c r="J60" s="52"/>
     </row>
     <row r="61" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A61" s="40"/>
+      <c r="B61" s="52"/>
+      <c r="C61" s="52"/>
+      <c r="D61" s="52"/>
+      <c r="E61" s="52"/>
+      <c r="F61" s="52"/>
       <c r="G61" s="4"/>
+      <c r="H61" s="52"/>
+      <c r="I61" s="52"/>
       <c r="J61" s="52"/>
     </row>
     <row r="62" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A62" s="40"/>
+      <c r="B62" s="52"/>
+      <c r="C62" s="52"/>
+      <c r="D62" s="52"/>
+      <c r="E62" s="52"/>
+      <c r="F62" s="52"/>
       <c r="G62" s="4"/>
+      <c r="H62" s="52"/>
+      <c r="I62" s="52"/>
       <c r="J62" s="52"/>
     </row>
     <row r="63" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
       <c r="A63" s="40"/>
+      <c r="B63" s="52"/>
+      <c r="C63" s="52"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="52"/>
+      <c r="F63" s="52"/>
       <c r="G63" s="4"/>
+      <c r="H63" s="52"/>
+      <c r="I63" s="52"/>
       <c r="J63" s="52"/>
     </row>
     <row r="64" spans="1:10" customHeight="1" ht="20.1" s="52" customFormat="1">
@@ -2714,6 +2835,8 @@
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="1"/>
+      <c r="H64" s="52"/>
+      <c r="I64" s="52"/>
       <c r="J64" s="52"/>
     </row>
   </sheetData>
